--- a/Result/profitability/6186.xlsx
+++ b/Result/profitability/6186.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7</v>
+        <v>1.69875</v>
       </c>
       <c r="N2" t="n">
-        <v>25.40875</v>
+        <v>26.86625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>1.74875</v>
+        <v>1.33125</v>
       </c>
       <c r="N3" t="n">
-        <v>25.5325</v>
+        <v>24.58625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1525</v>
+        <v>0.9112499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>20.76875</v>
+        <v>20.115</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6912499999999999</v>
+        <v>0.26625</v>
       </c>
       <c r="N5" t="n">
-        <v>13.1925</v>
+        <v>12.4525</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>-0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24125</v>
+        <v>-0.05875000000000005</v>
       </c>
       <c r="N6" t="n">
-        <v>10.41</v>
+        <v>9.766249999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05125000000000004</v>
+        <v>-0.06375000000000006</v>
       </c>
       <c r="N7" t="n">
-        <v>7.472499999999999</v>
+        <v>4.6375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08250000000000005</v>
+        <v>-0.3237500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4825</v>
+        <v>2.40875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>-0.57</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.415</v>
+        <v>-0.4150000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06749999999999984</v>
+        <v>0.06750000000000028</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.31125</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.90125</v>
+        <v>-0.9012499999999996</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1725</v>
+        <v>-0.1725000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-12.74125</v>
@@ -1899,7 +1899,7 @@
         <v>-0.19</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03750000000000001</v>
+        <v>-0.03750000000000007</v>
       </c>
       <c r="N12" t="n">
         <v>-10.8875</v>
@@ -2026,7 +2026,7 @@
         <v>-2.29</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.12375</v>
+        <v>-0.1237500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-13.35875</v>
@@ -9738,6 +9738,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>518</v>
+      </c>
+      <c r="D75" t="n">
+        <v>402</v>
+      </c>
+      <c r="E75" t="n">
+        <v>116</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>64</v>
+      </c>
+      <c r="K75" t="n">
+        <v>31</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.79875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.805</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9234449760765551</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0256968641114983</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9550561797752809</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.919999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.209261223047013</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
